--- a/frontend/test_data/header_detection/Wide_Invalid_Pivoted_Years_Test.xlsx
+++ b/frontend/test_data/header_detection/Wide_Invalid_Pivoted_Years_Test.xlsx
@@ -15288,7 +15288,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O201"/>
+  <dimension ref="A1:M201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15316,25 +15316,19 @@
         <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Search Booster (Pivoted)</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="J1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Duplicates Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="L1" t="str">
-        <v>FILLED CELLS</v>
+        <v>TOTAL RAW SCORE</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL RAW SCORE</v>
-      </c>
-      <c r="N1" t="str">
         <v>NORMALIZED SCORE (%)</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Unsupported Pivoted Penalty</v>
       </c>
     </row>
     <row r="2">
@@ -15363,25 +15357,19 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="M2">
-        <v>-34</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>-100</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -15398,37 +15386,31 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F3">
         <v>5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L3">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M3">
-        <v>-20</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -15445,37 +15427,31 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L4">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M4">
-        <v>-20</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -15492,37 +15468,31 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F5">
         <v>5</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L5">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M5">
-        <v>-20</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15539,37 +15509,31 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>5</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L6">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M6">
-        <v>-20</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15586,37 +15550,31 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L7">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M7">
-        <v>-20</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15633,37 +15591,31 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F8">
         <v>5</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L8">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M8">
-        <v>-20</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15680,37 +15632,31 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L9">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M9">
-        <v>-20</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15727,37 +15673,31 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F10">
         <v>5</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L10">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M10">
-        <v>-20</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15774,37 +15714,31 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F11">
         <v>5</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L11">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M11">
-        <v>-20</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15821,37 +15755,31 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>5</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L12">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M12">
-        <v>-20</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -15868,37 +15796,31 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F13">
         <v>5</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L13">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M13">
-        <v>-20</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -15915,37 +15837,31 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F14">
         <v>5</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L14">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M14">
-        <v>-20</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -15962,37 +15878,31 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>5</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L15">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M15">
-        <v>-20</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -16009,37 +15919,31 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>5</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L16">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M16">
-        <v>-20</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -16056,37 +15960,31 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F17">
         <v>5</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L17">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M17">
-        <v>-20</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -16103,37 +16001,31 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F18">
         <v>5</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L18">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M18">
-        <v>-20</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -16150,37 +16042,31 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F19">
         <v>5</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L19">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M19">
-        <v>-20</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -16197,37 +16083,31 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F20">
         <v>5</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L20">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M20">
-        <v>-20</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -16244,37 +16124,31 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F21">
         <v>5</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L21">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M21">
-        <v>-20</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -16291,37 +16165,31 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F22">
         <v>5</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L22">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M22">
-        <v>-20</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -16338,37 +16206,31 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F23">
         <v>5</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L23">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M23">
-        <v>-20</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -16385,37 +16247,31 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F24">
         <v>5</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L24">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M24">
-        <v>-20</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -16432,37 +16288,31 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F25">
         <v>5</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L25">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M25">
-        <v>-20</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -16479,37 +16329,31 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F26">
         <v>5</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L26">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M26">
-        <v>-20</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -16526,37 +16370,31 @@
         <v>0</v>
       </c>
       <c r="E27">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F27">
         <v>5</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L27">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M27">
-        <v>-20</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -16573,37 +16411,31 @@
         <v>0</v>
       </c>
       <c r="E28">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F28">
         <v>5</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L28">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M28">
-        <v>-20</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -16620,37 +16452,31 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F29">
         <v>5</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L29">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M29">
-        <v>-20</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -16667,37 +16493,31 @@
         <v>0</v>
       </c>
       <c r="E30">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F30">
         <v>5</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L30">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M30">
-        <v>-20</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -16714,37 +16534,31 @@
         <v>0</v>
       </c>
       <c r="E31">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F31">
         <v>5</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L31">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M31">
-        <v>-20</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -16761,37 +16575,31 @@
         <v>0</v>
       </c>
       <c r="E32">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F32">
         <v>5</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L32">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M32">
-        <v>-20</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -16808,37 +16616,31 @@
         <v>0</v>
       </c>
       <c r="E33">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F33">
         <v>5</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L33">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M33">
-        <v>-20</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -16855,37 +16657,31 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F34">
         <v>5</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L34">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M34">
-        <v>-20</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -16902,37 +16698,31 @@
         <v>0</v>
       </c>
       <c r="E35">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F35">
         <v>5</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L35">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M35">
-        <v>-20</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -16949,37 +16739,31 @@
         <v>0</v>
       </c>
       <c r="E36">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F36">
         <v>5</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L36">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M36">
-        <v>-20</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -16996,37 +16780,31 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F37">
         <v>5</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L37">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M37">
-        <v>-20</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -17043,37 +16821,31 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F38">
         <v>5</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L38">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M38">
-        <v>-20</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -17090,37 +16862,31 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F39">
         <v>5</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L39">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M39">
-        <v>-20</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -17137,37 +16903,31 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F40">
         <v>5</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L40">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M40">
-        <v>-20</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -17184,37 +16944,31 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F41">
         <v>5</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L41">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M41">
-        <v>-20</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -17231,37 +16985,31 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F42">
         <v>5</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
       <c r="I42">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L42">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M42">
-        <v>-20</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -17278,37 +17026,31 @@
         <v>0</v>
       </c>
       <c r="E43">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F43">
         <v>5</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L43">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M43">
-        <v>-20</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -17325,37 +17067,31 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F44">
         <v>5</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L44">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M44">
-        <v>-20</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -17372,37 +17108,31 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F45">
         <v>5</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L45">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M45">
-        <v>-20</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -17419,37 +17149,31 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F46">
         <v>5</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L46">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M46">
-        <v>-20</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -17466,37 +17190,31 @@
         <v>0</v>
       </c>
       <c r="E47">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F47">
         <v>5</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L47">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M47">
-        <v>-20</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -17513,37 +17231,31 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F48">
         <v>5</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
       <c r="I48">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L48">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M48">
-        <v>-20</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -17560,37 +17272,31 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F49">
         <v>5</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
       <c r="I49">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L49">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M49">
-        <v>-20</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -17607,37 +17313,31 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F50">
         <v>5</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H50">
         <v>0</v>
       </c>
       <c r="I50">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L50">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M50">
-        <v>-20</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -17654,37 +17354,31 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F51">
         <v>5</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
       <c r="I51">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L51">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M51">
-        <v>-20</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -17701,37 +17395,31 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F52">
         <v>5</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
       <c r="I52">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L52">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M52">
-        <v>-20</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -17748,37 +17436,31 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F53">
         <v>5</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
       <c r="I53">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L53">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M53">
-        <v>-20</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -17795,37 +17477,31 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F54">
         <v>5</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L54">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M54">
-        <v>-20</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -17842,37 +17518,31 @@
         <v>0</v>
       </c>
       <c r="E55">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F55">
         <v>5</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
       <c r="I55">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L55">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M55">
-        <v>-20</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -17889,37 +17559,31 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F56">
         <v>5</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
       <c r="I56">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L56">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M56">
-        <v>-20</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -17936,37 +17600,31 @@
         <v>0</v>
       </c>
       <c r="E57">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F57">
         <v>5</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
       <c r="I57">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L57">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M57">
-        <v>-20</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -17983,37 +17641,31 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F58">
         <v>5</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H58">
         <v>0</v>
       </c>
       <c r="I58">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J58">
         <v>0</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L58">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M58">
-        <v>-20</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -18030,37 +17682,31 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F59">
         <v>5</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L59">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M59">
-        <v>-20</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -18077,37 +17723,31 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F60">
         <v>5</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="I60">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L60">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M60">
-        <v>-20</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -18124,37 +17764,31 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F61">
         <v>5</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
       <c r="I61">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L61">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M61">
-        <v>-20</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -18171,37 +17805,31 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F62">
         <v>5</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
       <c r="I62">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L62">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M62">
-        <v>-20</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -18218,37 +17846,31 @@
         <v>0</v>
       </c>
       <c r="E63">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F63">
         <v>5</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H63">
         <v>0</v>
       </c>
       <c r="I63">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L63">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M63">
-        <v>-20</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -18265,37 +17887,31 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F64">
         <v>5</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H64">
         <v>0</v>
       </c>
       <c r="I64">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J64">
         <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L64">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M64">
-        <v>-20</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -18312,37 +17928,31 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F65">
         <v>5</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H65">
         <v>0</v>
       </c>
       <c r="I65">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L65">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M65">
-        <v>-20</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -18359,37 +17969,31 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F66">
         <v>5</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H66">
         <v>0</v>
       </c>
       <c r="I66">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L66">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M66">
-        <v>-20</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -18406,37 +18010,31 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F67">
         <v>5</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H67">
         <v>0</v>
       </c>
       <c r="I67">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L67">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M67">
-        <v>-20</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -18453,37 +18051,31 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F68">
         <v>5</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H68">
         <v>0</v>
       </c>
       <c r="I68">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L68">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M68">
-        <v>-20</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -18500,37 +18092,31 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F69">
         <v>5</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H69">
         <v>0</v>
       </c>
       <c r="I69">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L69">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M69">
-        <v>-20</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -18547,37 +18133,31 @@
         <v>0</v>
       </c>
       <c r="E70">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F70">
         <v>5</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H70">
         <v>0</v>
       </c>
       <c r="I70">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J70">
         <v>0</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L70">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M70">
-        <v>-20</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -18594,37 +18174,31 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F71">
         <v>5</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H71">
         <v>0</v>
       </c>
       <c r="I71">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L71">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M71">
-        <v>-20</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -18641,37 +18215,31 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F72">
         <v>5</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H72">
         <v>0</v>
       </c>
       <c r="I72">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L72">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M72">
-        <v>-20</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -18688,37 +18256,31 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F73">
         <v>5</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H73">
         <v>0</v>
       </c>
       <c r="I73">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L73">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M73">
-        <v>-20</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -18735,37 +18297,31 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F74">
         <v>5</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H74">
         <v>0</v>
       </c>
       <c r="I74">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J74">
         <v>0</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L74">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M74">
-        <v>-20</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -18782,37 +18338,31 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F75">
         <v>5</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
       <c r="I75">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L75">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M75">
-        <v>-20</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -18829,37 +18379,31 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F76">
         <v>5</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
       <c r="I76">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J76">
         <v>0</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L76">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M76">
-        <v>-20</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -18876,37 +18420,31 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F77">
         <v>5</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H77">
         <v>0</v>
       </c>
       <c r="I77">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J77">
         <v>0</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L77">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M77">
-        <v>-20</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -18923,37 +18461,31 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F78">
         <v>5</v>
       </c>
       <c r="G78">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H78">
         <v>0</v>
       </c>
       <c r="I78">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L78">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M78">
-        <v>-20</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -18970,37 +18502,31 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F79">
         <v>5</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H79">
         <v>0</v>
       </c>
       <c r="I79">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L79">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M79">
-        <v>-20</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -19017,37 +18543,31 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F80">
         <v>5</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H80">
         <v>0</v>
       </c>
       <c r="I80">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L80">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M80">
-        <v>-20</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -19064,37 +18584,31 @@
         <v>0</v>
       </c>
       <c r="E81">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F81">
         <v>5</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H81">
         <v>0</v>
       </c>
       <c r="I81">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L81">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M81">
-        <v>-20</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -19111,37 +18625,31 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F82">
         <v>5</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H82">
         <v>0</v>
       </c>
       <c r="I82">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L82">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M82">
-        <v>-20</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -19158,37 +18666,31 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F83">
         <v>5</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H83">
         <v>0</v>
       </c>
       <c r="I83">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L83">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M83">
-        <v>-20</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -19205,37 +18707,31 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F84">
         <v>5</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H84">
         <v>0</v>
       </c>
       <c r="I84">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L84">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M84">
-        <v>-20</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -19252,37 +18748,31 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F85">
         <v>5</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H85">
         <v>0</v>
       </c>
       <c r="I85">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L85">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M85">
-        <v>-20</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -19299,37 +18789,31 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F86">
         <v>5</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H86">
         <v>0</v>
       </c>
       <c r="I86">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L86">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M86">
-        <v>-20</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -19346,37 +18830,31 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F87">
         <v>5</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H87">
         <v>0</v>
       </c>
       <c r="I87">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L87">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M87">
-        <v>-20</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -19393,37 +18871,31 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F88">
         <v>5</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L88">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M88">
-        <v>-20</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -19440,37 +18912,31 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F89">
         <v>5</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H89">
         <v>0</v>
       </c>
       <c r="I89">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L89">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M89">
-        <v>-20</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -19487,37 +18953,31 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F90">
         <v>5</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H90">
         <v>0</v>
       </c>
       <c r="I90">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L90">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M90">
-        <v>-20</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -19534,37 +18994,31 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F91">
         <v>5</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H91">
         <v>0</v>
       </c>
       <c r="I91">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L91">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M91">
-        <v>-20</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -19581,37 +19035,31 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F92">
         <v>5</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H92">
         <v>0</v>
       </c>
       <c r="I92">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L92">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M92">
-        <v>-20</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -19628,37 +19076,31 @@
         <v>0</v>
       </c>
       <c r="E93">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F93">
         <v>5</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H93">
         <v>0</v>
       </c>
       <c r="I93">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L93">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M93">
-        <v>-20</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -19675,37 +19117,31 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F94">
         <v>5</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H94">
         <v>0</v>
       </c>
       <c r="I94">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L94">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M94">
-        <v>-20</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
-      <c r="O94">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -19722,37 +19158,31 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F95">
         <v>5</v>
       </c>
       <c r="G95">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H95">
         <v>0</v>
       </c>
       <c r="I95">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L95">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M95">
-        <v>-20</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -19769,37 +19199,31 @@
         <v>0</v>
       </c>
       <c r="E96">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F96">
         <v>5</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H96">
         <v>0</v>
       </c>
       <c r="I96">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L96">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M96">
-        <v>-20</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -19816,37 +19240,31 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F97">
         <v>5</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H97">
         <v>0</v>
       </c>
       <c r="I97">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L97">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M97">
-        <v>-20</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -19863,37 +19281,31 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F98">
         <v>5</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H98">
         <v>0</v>
       </c>
       <c r="I98">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L98">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M98">
-        <v>-20</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -19910,37 +19322,31 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F99">
         <v>5</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H99">
         <v>0</v>
       </c>
       <c r="I99">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L99">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M99">
-        <v>-20</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
-      <c r="O99">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -19957,37 +19363,31 @@
         <v>0</v>
       </c>
       <c r="E100">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F100">
         <v>5</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H100">
         <v>0</v>
       </c>
       <c r="I100">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L100">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M100">
-        <v>-20</v>
-      </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
-      <c r="O100">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -20004,37 +19404,31 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F101">
         <v>5</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H101">
         <v>0</v>
       </c>
       <c r="I101">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L101">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M101">
-        <v>-20</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -20051,37 +19445,31 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F102">
         <v>5</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H102">
         <v>0</v>
       </c>
       <c r="I102">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L102">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M102">
-        <v>-20</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -20098,37 +19486,31 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F103">
         <v>5</v>
       </c>
       <c r="G103">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H103">
         <v>0</v>
       </c>
       <c r="I103">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L103">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M103">
-        <v>-20</v>
-      </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -20145,37 +19527,31 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F104">
         <v>5</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H104">
         <v>0</v>
       </c>
       <c r="I104">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L104">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M104">
-        <v>-20</v>
-      </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
-      <c r="O104">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -20192,37 +19568,31 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F105">
         <v>5</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H105">
         <v>0</v>
       </c>
       <c r="I105">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J105">
         <v>0</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L105">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M105">
-        <v>-20</v>
-      </c>
-      <c r="N105">
-        <v>0</v>
-      </c>
-      <c r="O105">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -20239,37 +19609,31 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F106">
         <v>5</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H106">
         <v>0</v>
       </c>
       <c r="I106">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L106">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M106">
-        <v>-20</v>
-      </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
-      <c r="O106">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -20286,37 +19650,31 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F107">
         <v>5</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H107">
         <v>0</v>
       </c>
       <c r="I107">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L107">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M107">
-        <v>-20</v>
-      </c>
-      <c r="N107">
-        <v>0</v>
-      </c>
-      <c r="O107">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -20333,37 +19691,31 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F108">
         <v>5</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H108">
         <v>0</v>
       </c>
       <c r="I108">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L108">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M108">
-        <v>-20</v>
-      </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
-      <c r="O108">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -20380,37 +19732,31 @@
         <v>0</v>
       </c>
       <c r="E109">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F109">
         <v>5</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H109">
         <v>0</v>
       </c>
       <c r="I109">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L109">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M109">
-        <v>-20</v>
-      </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
-      <c r="O109">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -20427,37 +19773,31 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F110">
         <v>5</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H110">
         <v>0</v>
       </c>
       <c r="I110">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J110">
         <v>0</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L110">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M110">
-        <v>-20</v>
-      </c>
-      <c r="N110">
-        <v>0</v>
-      </c>
-      <c r="O110">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -20474,37 +19814,31 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F111">
         <v>5</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H111">
         <v>0</v>
       </c>
       <c r="I111">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L111">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M111">
-        <v>-20</v>
-      </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
-      <c r="O111">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -20521,37 +19855,31 @@
         <v>0</v>
       </c>
       <c r="E112">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F112">
         <v>5</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H112">
         <v>0</v>
       </c>
       <c r="I112">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L112">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M112">
-        <v>-20</v>
-      </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="O112">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -20568,37 +19896,31 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F113">
         <v>5</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H113">
         <v>0</v>
       </c>
       <c r="I113">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L113">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M113">
-        <v>-20</v>
-      </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
-      <c r="O113">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -20615,37 +19937,31 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F114">
         <v>5</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H114">
         <v>0</v>
       </c>
       <c r="I114">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L114">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M114">
-        <v>-20</v>
-      </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
-      <c r="O114">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -20662,37 +19978,31 @@
         <v>0</v>
       </c>
       <c r="E115">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F115">
         <v>5</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H115">
         <v>0</v>
       </c>
       <c r="I115">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L115">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M115">
-        <v>-20</v>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -20709,37 +20019,31 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F116">
         <v>5</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H116">
         <v>0</v>
       </c>
       <c r="I116">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L116">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M116">
-        <v>-20</v>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -20756,37 +20060,31 @@
         <v>0</v>
       </c>
       <c r="E117">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F117">
         <v>5</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H117">
         <v>0</v>
       </c>
       <c r="I117">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L117">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M117">
-        <v>-20</v>
-      </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -20803,37 +20101,31 @@
         <v>0</v>
       </c>
       <c r="E118">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F118">
         <v>5</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H118">
         <v>0</v>
       </c>
       <c r="I118">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L118">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M118">
-        <v>-20</v>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -20850,37 +20142,31 @@
         <v>0</v>
       </c>
       <c r="E119">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F119">
         <v>5</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H119">
         <v>0</v>
       </c>
       <c r="I119">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L119">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M119">
-        <v>-20</v>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -20897,37 +20183,31 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F120">
         <v>5</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H120">
         <v>0</v>
       </c>
       <c r="I120">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J120">
         <v>0</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L120">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M120">
-        <v>-20</v>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -20944,37 +20224,31 @@
         <v>0</v>
       </c>
       <c r="E121">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F121">
         <v>5</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H121">
         <v>0</v>
       </c>
       <c r="I121">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L121">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M121">
-        <v>-20</v>
-      </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -20991,37 +20265,31 @@
         <v>0</v>
       </c>
       <c r="E122">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F122">
         <v>5</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H122">
         <v>0</v>
       </c>
       <c r="I122">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L122">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M122">
-        <v>-20</v>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -21038,37 +20306,31 @@
         <v>0</v>
       </c>
       <c r="E123">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F123">
         <v>5</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H123">
         <v>0</v>
       </c>
       <c r="I123">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L123">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M123">
-        <v>-20</v>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -21085,37 +20347,31 @@
         <v>0</v>
       </c>
       <c r="E124">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F124">
         <v>5</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H124">
         <v>0</v>
       </c>
       <c r="I124">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L124">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M124">
-        <v>-20</v>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -21132,37 +20388,31 @@
         <v>0</v>
       </c>
       <c r="E125">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F125">
         <v>5</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H125">
         <v>0</v>
       </c>
       <c r="I125">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J125">
         <v>0</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L125">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M125">
-        <v>-20</v>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -21179,37 +20429,31 @@
         <v>0</v>
       </c>
       <c r="E126">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F126">
         <v>5</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H126">
         <v>0</v>
       </c>
       <c r="I126">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J126">
         <v>0</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L126">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M126">
-        <v>-20</v>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -21226,37 +20470,31 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F127">
         <v>5</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H127">
         <v>0</v>
       </c>
       <c r="I127">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J127">
         <v>0</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L127">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M127">
-        <v>-20</v>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -21273,37 +20511,31 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F128">
         <v>5</v>
       </c>
       <c r="G128">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H128">
         <v>0</v>
       </c>
       <c r="I128">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L128">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M128">
-        <v>-20</v>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -21320,37 +20552,31 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F129">
         <v>5</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H129">
         <v>0</v>
       </c>
       <c r="I129">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L129">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M129">
-        <v>-20</v>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -21367,37 +20593,31 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F130">
         <v>5</v>
       </c>
       <c r="G130">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H130">
         <v>0</v>
       </c>
       <c r="I130">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L130">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M130">
-        <v>-20</v>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -21414,37 +20634,31 @@
         <v>0</v>
       </c>
       <c r="E131">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F131">
         <v>5</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H131">
         <v>0</v>
       </c>
       <c r="I131">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J131">
         <v>0</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L131">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M131">
-        <v>-20</v>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -21461,37 +20675,31 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F132">
         <v>5</v>
       </c>
       <c r="G132">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H132">
         <v>0</v>
       </c>
       <c r="I132">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J132">
         <v>0</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L132">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M132">
-        <v>-20</v>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -21508,37 +20716,31 @@
         <v>0</v>
       </c>
       <c r="E133">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F133">
         <v>5</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J133">
         <v>0</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L133">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M133">
-        <v>-20</v>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -21555,37 +20757,31 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F134">
         <v>5</v>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H134">
         <v>0</v>
       </c>
       <c r="I134">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L134">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M134">
-        <v>-20</v>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -21602,37 +20798,31 @@
         <v>0</v>
       </c>
       <c r="E135">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F135">
         <v>5</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H135">
         <v>0</v>
       </c>
       <c r="I135">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L135">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M135">
-        <v>-20</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
@@ -21649,37 +20839,31 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F136">
         <v>5</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H136">
         <v>0</v>
       </c>
       <c r="I136">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J136">
         <v>0</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L136">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M136">
-        <v>-20</v>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -21696,37 +20880,31 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F137">
         <v>5</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H137">
         <v>0</v>
       </c>
       <c r="I137">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J137">
         <v>0</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L137">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M137">
-        <v>-20</v>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -21743,37 +20921,31 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F138">
         <v>5</v>
       </c>
       <c r="G138">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L138">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M138">
-        <v>-20</v>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -21790,37 +20962,31 @@
         <v>0</v>
       </c>
       <c r="E139">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F139">
         <v>5</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H139">
         <v>0</v>
       </c>
       <c r="I139">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L139">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M139">
-        <v>-20</v>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -21837,37 +21003,31 @@
         <v>0</v>
       </c>
       <c r="E140">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F140">
         <v>5</v>
       </c>
       <c r="G140">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H140">
         <v>0</v>
       </c>
       <c r="I140">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L140">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M140">
-        <v>-20</v>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -21884,37 +21044,31 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F141">
         <v>5</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H141">
         <v>0</v>
       </c>
       <c r="I141">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L141">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M141">
-        <v>-20</v>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -21931,37 +21085,31 @@
         <v>0</v>
       </c>
       <c r="E142">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F142">
         <v>5</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H142">
         <v>0</v>
       </c>
       <c r="I142">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L142">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M142">
-        <v>-20</v>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -21978,37 +21126,31 @@
         <v>0</v>
       </c>
       <c r="E143">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F143">
         <v>5</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H143">
         <v>0</v>
       </c>
       <c r="I143">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L143">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M143">
-        <v>-20</v>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -22025,37 +21167,31 @@
         <v>0</v>
       </c>
       <c r="E144">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F144">
         <v>5</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H144">
         <v>0</v>
       </c>
       <c r="I144">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J144">
         <v>0</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L144">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M144">
-        <v>-20</v>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -22072,37 +21208,31 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F145">
         <v>5</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H145">
         <v>0</v>
       </c>
       <c r="I145">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L145">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M145">
-        <v>-20</v>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -22119,37 +21249,31 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F146">
         <v>5</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H146">
         <v>0</v>
       </c>
       <c r="I146">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J146">
         <v>0</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L146">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M146">
-        <v>-20</v>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -22166,37 +21290,31 @@
         <v>0</v>
       </c>
       <c r="E147">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F147">
         <v>5</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H147">
         <v>0</v>
       </c>
       <c r="I147">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L147">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M147">
-        <v>-20</v>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -22213,37 +21331,31 @@
         <v>0</v>
       </c>
       <c r="E148">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F148">
         <v>5</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H148">
         <v>0</v>
       </c>
       <c r="I148">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L148">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M148">
-        <v>-20</v>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="O148">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -22260,37 +21372,31 @@
         <v>0</v>
       </c>
       <c r="E149">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F149">
         <v>5</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H149">
         <v>0</v>
       </c>
       <c r="I149">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J149">
         <v>0</v>
       </c>
       <c r="K149">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L149">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M149">
-        <v>-20</v>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="O149">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -22307,37 +21413,31 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F150">
         <v>5</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H150">
         <v>0</v>
       </c>
       <c r="I150">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J150">
         <v>0</v>
       </c>
       <c r="K150">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L150">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M150">
-        <v>-20</v>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -22354,37 +21454,31 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F151">
         <v>5</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H151">
         <v>0</v>
       </c>
       <c r="I151">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J151">
         <v>0</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L151">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M151">
-        <v>-20</v>
-      </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="O151">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -22401,37 +21495,31 @@
         <v>0</v>
       </c>
       <c r="E152">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F152">
         <v>5</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H152">
         <v>0</v>
       </c>
       <c r="I152">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J152">
         <v>0</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L152">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M152">
-        <v>-20</v>
-      </c>
-      <c r="N152">
-        <v>0</v>
-      </c>
-      <c r="O152">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -22448,37 +21536,31 @@
         <v>0</v>
       </c>
       <c r="E153">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F153">
         <v>5</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H153">
         <v>0</v>
       </c>
       <c r="I153">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J153">
         <v>0</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L153">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M153">
-        <v>-20</v>
-      </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
-      <c r="O153">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -22495,37 +21577,31 @@
         <v>0</v>
       </c>
       <c r="E154">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F154">
         <v>5</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H154">
         <v>0</v>
       </c>
       <c r="I154">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J154">
         <v>0</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L154">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M154">
-        <v>-20</v>
-      </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
-      <c r="O154">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -22542,37 +21618,31 @@
         <v>0</v>
       </c>
       <c r="E155">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F155">
         <v>5</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J155">
         <v>0</v>
       </c>
       <c r="K155">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L155">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M155">
-        <v>-20</v>
-      </c>
-      <c r="N155">
-        <v>0</v>
-      </c>
-      <c r="O155">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -22589,37 +21659,31 @@
         <v>0</v>
       </c>
       <c r="E156">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F156">
         <v>5</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H156">
         <v>0</v>
       </c>
       <c r="I156">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J156">
         <v>0</v>
       </c>
       <c r="K156">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L156">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M156">
-        <v>-20</v>
-      </c>
-      <c r="N156">
-        <v>0</v>
-      </c>
-      <c r="O156">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -22636,37 +21700,31 @@
         <v>0</v>
       </c>
       <c r="E157">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F157">
         <v>5</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H157">
         <v>0</v>
       </c>
       <c r="I157">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J157">
         <v>0</v>
       </c>
       <c r="K157">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L157">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M157">
-        <v>-20</v>
-      </c>
-      <c r="N157">
-        <v>0</v>
-      </c>
-      <c r="O157">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -22683,37 +21741,31 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F158">
         <v>5</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H158">
         <v>0</v>
       </c>
       <c r="I158">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J158">
         <v>0</v>
       </c>
       <c r="K158">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L158">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M158">
-        <v>-20</v>
-      </c>
-      <c r="N158">
-        <v>0</v>
-      </c>
-      <c r="O158">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -22730,37 +21782,31 @@
         <v>0</v>
       </c>
       <c r="E159">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F159">
         <v>5</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H159">
         <v>0</v>
       </c>
       <c r="I159">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J159">
         <v>0</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L159">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M159">
-        <v>-20</v>
-      </c>
-      <c r="N159">
-        <v>0</v>
-      </c>
-      <c r="O159">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -22777,37 +21823,31 @@
         <v>0</v>
       </c>
       <c r="E160">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F160">
         <v>5</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H160">
         <v>0</v>
       </c>
       <c r="I160">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J160">
         <v>0</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L160">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M160">
-        <v>-20</v>
-      </c>
-      <c r="N160">
-        <v>0</v>
-      </c>
-      <c r="O160">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -22824,37 +21864,31 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F161">
         <v>5</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H161">
         <v>0</v>
       </c>
       <c r="I161">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J161">
         <v>0</v>
       </c>
       <c r="K161">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L161">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M161">
-        <v>-20</v>
-      </c>
-      <c r="N161">
-        <v>0</v>
-      </c>
-      <c r="O161">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -22871,37 +21905,31 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F162">
         <v>5</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H162">
         <v>0</v>
       </c>
       <c r="I162">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J162">
         <v>0</v>
       </c>
       <c r="K162">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L162">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M162">
-        <v>-20</v>
-      </c>
-      <c r="N162">
-        <v>0</v>
-      </c>
-      <c r="O162">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -22918,37 +21946,31 @@
         <v>0</v>
       </c>
       <c r="E163">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F163">
         <v>5</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H163">
         <v>0</v>
       </c>
       <c r="I163">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J163">
         <v>0</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L163">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M163">
-        <v>-20</v>
-      </c>
-      <c r="N163">
-        <v>0</v>
-      </c>
-      <c r="O163">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -22965,37 +21987,31 @@
         <v>0</v>
       </c>
       <c r="E164">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F164">
         <v>5</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H164">
         <v>0</v>
       </c>
       <c r="I164">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J164">
         <v>0</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L164">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M164">
-        <v>-20</v>
-      </c>
-      <c r="N164">
-        <v>0</v>
-      </c>
-      <c r="O164">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -23012,37 +22028,31 @@
         <v>0</v>
       </c>
       <c r="E165">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F165">
         <v>5</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H165">
         <v>0</v>
       </c>
       <c r="I165">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J165">
         <v>0</v>
       </c>
       <c r="K165">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L165">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M165">
-        <v>-20</v>
-      </c>
-      <c r="N165">
-        <v>0</v>
-      </c>
-      <c r="O165">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -23059,37 +22069,31 @@
         <v>0</v>
       </c>
       <c r="E166">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F166">
         <v>5</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H166">
         <v>0</v>
       </c>
       <c r="I166">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J166">
         <v>0</v>
       </c>
       <c r="K166">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L166">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M166">
-        <v>-20</v>
-      </c>
-      <c r="N166">
-        <v>0</v>
-      </c>
-      <c r="O166">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -23106,37 +22110,31 @@
         <v>0</v>
       </c>
       <c r="E167">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F167">
         <v>5</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H167">
         <v>0</v>
       </c>
       <c r="I167">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J167">
         <v>0</v>
       </c>
       <c r="K167">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L167">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M167">
-        <v>-20</v>
-      </c>
-      <c r="N167">
-        <v>0</v>
-      </c>
-      <c r="O167">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -23153,37 +22151,31 @@
         <v>0</v>
       </c>
       <c r="E168">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F168">
         <v>5</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H168">
         <v>0</v>
       </c>
       <c r="I168">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J168">
         <v>0</v>
       </c>
       <c r="K168">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L168">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M168">
-        <v>-20</v>
-      </c>
-      <c r="N168">
-        <v>0</v>
-      </c>
-      <c r="O168">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -23200,37 +22192,31 @@
         <v>0</v>
       </c>
       <c r="E169">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F169">
         <v>5</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H169">
         <v>0</v>
       </c>
       <c r="I169">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J169">
         <v>0</v>
       </c>
       <c r="K169">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L169">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M169">
-        <v>-20</v>
-      </c>
-      <c r="N169">
-        <v>0</v>
-      </c>
-      <c r="O169">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -23247,37 +22233,31 @@
         <v>0</v>
       </c>
       <c r="E170">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F170">
         <v>5</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H170">
         <v>0</v>
       </c>
       <c r="I170">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J170">
         <v>0</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L170">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M170">
-        <v>-20</v>
-      </c>
-      <c r="N170">
-        <v>0</v>
-      </c>
-      <c r="O170">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -23294,37 +22274,31 @@
         <v>0</v>
       </c>
       <c r="E171">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F171">
         <v>5</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H171">
         <v>0</v>
       </c>
       <c r="I171">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J171">
         <v>0</v>
       </c>
       <c r="K171">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L171">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M171">
-        <v>-20</v>
-      </c>
-      <c r="N171">
-        <v>0</v>
-      </c>
-      <c r="O171">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -23341,37 +22315,31 @@
         <v>0</v>
       </c>
       <c r="E172">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F172">
         <v>5</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J172">
         <v>0</v>
       </c>
       <c r="K172">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L172">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M172">
-        <v>-20</v>
-      </c>
-      <c r="N172">
-        <v>0</v>
-      </c>
-      <c r="O172">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -23388,37 +22356,31 @@
         <v>0</v>
       </c>
       <c r="E173">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F173">
         <v>5</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H173">
         <v>0</v>
       </c>
       <c r="I173">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J173">
         <v>0</v>
       </c>
       <c r="K173">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L173">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M173">
-        <v>-20</v>
-      </c>
-      <c r="N173">
-        <v>0</v>
-      </c>
-      <c r="O173">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -23435,37 +22397,31 @@
         <v>0</v>
       </c>
       <c r="E174">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F174">
         <v>5</v>
       </c>
       <c r="G174">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H174">
         <v>0</v>
       </c>
       <c r="I174">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J174">
         <v>0</v>
       </c>
       <c r="K174">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L174">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M174">
-        <v>-20</v>
-      </c>
-      <c r="N174">
-        <v>0</v>
-      </c>
-      <c r="O174">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -23482,37 +22438,31 @@
         <v>0</v>
       </c>
       <c r="E175">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F175">
         <v>5</v>
       </c>
       <c r="G175">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H175">
         <v>0</v>
       </c>
       <c r="I175">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J175">
         <v>0</v>
       </c>
       <c r="K175">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L175">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M175">
-        <v>-20</v>
-      </c>
-      <c r="N175">
-        <v>0</v>
-      </c>
-      <c r="O175">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -23529,37 +22479,31 @@
         <v>0</v>
       </c>
       <c r="E176">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F176">
         <v>5</v>
       </c>
       <c r="G176">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H176">
         <v>0</v>
       </c>
       <c r="I176">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J176">
         <v>0</v>
       </c>
       <c r="K176">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L176">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M176">
-        <v>-20</v>
-      </c>
-      <c r="N176">
-        <v>0</v>
-      </c>
-      <c r="O176">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -23576,37 +22520,31 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F177">
         <v>5</v>
       </c>
       <c r="G177">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H177">
         <v>0</v>
       </c>
       <c r="I177">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J177">
         <v>0</v>
       </c>
       <c r="K177">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L177">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M177">
-        <v>-20</v>
-      </c>
-      <c r="N177">
-        <v>0</v>
-      </c>
-      <c r="O177">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -23623,37 +22561,31 @@
         <v>0</v>
       </c>
       <c r="E178">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F178">
         <v>5</v>
       </c>
       <c r="G178">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H178">
         <v>0</v>
       </c>
       <c r="I178">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J178">
         <v>0</v>
       </c>
       <c r="K178">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L178">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M178">
-        <v>-20</v>
-      </c>
-      <c r="N178">
-        <v>0</v>
-      </c>
-      <c r="O178">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -23670,37 +22602,31 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F179">
         <v>5</v>
       </c>
       <c r="G179">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H179">
         <v>0</v>
       </c>
       <c r="I179">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J179">
         <v>0</v>
       </c>
       <c r="K179">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L179">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M179">
-        <v>-20</v>
-      </c>
-      <c r="N179">
-        <v>0</v>
-      </c>
-      <c r="O179">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -23717,37 +22643,31 @@
         <v>0</v>
       </c>
       <c r="E180">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F180">
         <v>5</v>
       </c>
       <c r="G180">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H180">
         <v>0</v>
       </c>
       <c r="I180">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J180">
         <v>0</v>
       </c>
       <c r="K180">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L180">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M180">
-        <v>-20</v>
-      </c>
-      <c r="N180">
-        <v>0</v>
-      </c>
-      <c r="O180">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -23764,37 +22684,31 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F181">
         <v>5</v>
       </c>
       <c r="G181">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H181">
         <v>0</v>
       </c>
       <c r="I181">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J181">
         <v>0</v>
       </c>
       <c r="K181">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L181">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M181">
-        <v>-20</v>
-      </c>
-      <c r="N181">
-        <v>0</v>
-      </c>
-      <c r="O181">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -23811,37 +22725,31 @@
         <v>0</v>
       </c>
       <c r="E182">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F182">
         <v>5</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H182">
         <v>0</v>
       </c>
       <c r="I182">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J182">
         <v>0</v>
       </c>
       <c r="K182">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L182">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M182">
-        <v>-20</v>
-      </c>
-      <c r="N182">
-        <v>0</v>
-      </c>
-      <c r="O182">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -23858,37 +22766,31 @@
         <v>0</v>
       </c>
       <c r="E183">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F183">
         <v>5</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H183">
         <v>0</v>
       </c>
       <c r="I183">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J183">
         <v>0</v>
       </c>
       <c r="K183">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L183">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M183">
-        <v>-20</v>
-      </c>
-      <c r="N183">
-        <v>0</v>
-      </c>
-      <c r="O183">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -23905,37 +22807,31 @@
         <v>0</v>
       </c>
       <c r="E184">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F184">
         <v>5</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H184">
         <v>0</v>
       </c>
       <c r="I184">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J184">
         <v>0</v>
       </c>
       <c r="K184">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L184">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M184">
-        <v>-20</v>
-      </c>
-      <c r="N184">
-        <v>0</v>
-      </c>
-      <c r="O184">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -23952,37 +22848,31 @@
         <v>0</v>
       </c>
       <c r="E185">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F185">
         <v>5</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H185">
         <v>0</v>
       </c>
       <c r="I185">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J185">
         <v>0</v>
       </c>
       <c r="K185">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L185">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M185">
-        <v>-20</v>
-      </c>
-      <c r="N185">
-        <v>0</v>
-      </c>
-      <c r="O185">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -23999,37 +22889,31 @@
         <v>0</v>
       </c>
       <c r="E186">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F186">
         <v>5</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H186">
         <v>0</v>
       </c>
       <c r="I186">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J186">
         <v>0</v>
       </c>
       <c r="K186">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L186">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M186">
-        <v>-20</v>
-      </c>
-      <c r="N186">
-        <v>0</v>
-      </c>
-      <c r="O186">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -24046,37 +22930,31 @@
         <v>0</v>
       </c>
       <c r="E187">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F187">
         <v>5</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H187">
         <v>0</v>
       </c>
       <c r="I187">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J187">
         <v>0</v>
       </c>
       <c r="K187">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L187">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M187">
-        <v>-20</v>
-      </c>
-      <c r="N187">
-        <v>0</v>
-      </c>
-      <c r="O187">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -24093,37 +22971,31 @@
         <v>0</v>
       </c>
       <c r="E188">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F188">
         <v>5</v>
       </c>
       <c r="G188">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H188">
         <v>0</v>
       </c>
       <c r="I188">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J188">
         <v>0</v>
       </c>
       <c r="K188">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L188">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M188">
-        <v>-20</v>
-      </c>
-      <c r="N188">
-        <v>0</v>
-      </c>
-      <c r="O188">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -24140,37 +23012,31 @@
         <v>0</v>
       </c>
       <c r="E189">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F189">
         <v>5</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H189">
         <v>0</v>
       </c>
       <c r="I189">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J189">
         <v>0</v>
       </c>
       <c r="K189">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L189">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M189">
-        <v>-20</v>
-      </c>
-      <c r="N189">
-        <v>0</v>
-      </c>
-      <c r="O189">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -24187,37 +23053,31 @@
         <v>0</v>
       </c>
       <c r="E190">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F190">
         <v>5</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H190">
         <v>0</v>
       </c>
       <c r="I190">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J190">
         <v>0</v>
       </c>
       <c r="K190">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L190">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M190">
-        <v>-20</v>
-      </c>
-      <c r="N190">
-        <v>0</v>
-      </c>
-      <c r="O190">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -24234,37 +23094,31 @@
         <v>0</v>
       </c>
       <c r="E191">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F191">
         <v>5</v>
       </c>
       <c r="G191">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H191">
         <v>0</v>
       </c>
       <c r="I191">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J191">
         <v>0</v>
       </c>
       <c r="K191">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L191">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M191">
-        <v>-20</v>
-      </c>
-      <c r="N191">
-        <v>0</v>
-      </c>
-      <c r="O191">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -24281,37 +23135,31 @@
         <v>0</v>
       </c>
       <c r="E192">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F192">
         <v>5</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H192">
         <v>0</v>
       </c>
       <c r="I192">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J192">
         <v>0</v>
       </c>
       <c r="K192">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L192">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M192">
-        <v>-20</v>
-      </c>
-      <c r="N192">
-        <v>0</v>
-      </c>
-      <c r="O192">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -24328,37 +23176,31 @@
         <v>0</v>
       </c>
       <c r="E193">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F193">
         <v>5</v>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H193">
         <v>0</v>
       </c>
       <c r="I193">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J193">
         <v>0</v>
       </c>
       <c r="K193">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L193">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M193">
-        <v>-20</v>
-      </c>
-      <c r="N193">
-        <v>0</v>
-      </c>
-      <c r="O193">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -24375,37 +23217,31 @@
         <v>0</v>
       </c>
       <c r="E194">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F194">
         <v>5</v>
       </c>
       <c r="G194">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H194">
         <v>0</v>
       </c>
       <c r="I194">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J194">
         <v>0</v>
       </c>
       <c r="K194">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L194">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M194">
-        <v>-20</v>
-      </c>
-      <c r="N194">
-        <v>0</v>
-      </c>
-      <c r="O194">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -24422,37 +23258,31 @@
         <v>0</v>
       </c>
       <c r="E195">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F195">
         <v>5</v>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H195">
         <v>0</v>
       </c>
       <c r="I195">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J195">
         <v>0</v>
       </c>
       <c r="K195">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L195">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M195">
-        <v>-20</v>
-      </c>
-      <c r="N195">
-        <v>0</v>
-      </c>
-      <c r="O195">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -24469,37 +23299,31 @@
         <v>0</v>
       </c>
       <c r="E196">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F196">
         <v>5</v>
       </c>
       <c r="G196">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H196">
         <v>0</v>
       </c>
       <c r="I196">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J196">
         <v>0</v>
       </c>
       <c r="K196">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L196">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M196">
-        <v>-20</v>
-      </c>
-      <c r="N196">
-        <v>0</v>
-      </c>
-      <c r="O196">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -24516,37 +23340,31 @@
         <v>0</v>
       </c>
       <c r="E197">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F197">
         <v>5</v>
       </c>
       <c r="G197">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H197">
         <v>0</v>
       </c>
       <c r="I197">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J197">
         <v>0</v>
       </c>
       <c r="K197">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L197">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M197">
-        <v>-20</v>
-      </c>
-      <c r="N197">
-        <v>0</v>
-      </c>
-      <c r="O197">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -24563,37 +23381,31 @@
         <v>0</v>
       </c>
       <c r="E198">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F198">
         <v>5</v>
       </c>
       <c r="G198">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H198">
         <v>0</v>
       </c>
       <c r="I198">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J198">
         <v>0</v>
       </c>
       <c r="K198">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L198">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M198">
-        <v>-20</v>
-      </c>
-      <c r="N198">
-        <v>0</v>
-      </c>
-      <c r="O198">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -24610,37 +23422,31 @@
         <v>0</v>
       </c>
       <c r="E199">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F199">
         <v>5</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H199">
         <v>0</v>
       </c>
       <c r="I199">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J199">
         <v>0</v>
       </c>
       <c r="K199">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L199">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M199">
-        <v>-20</v>
-      </c>
-      <c r="N199">
-        <v>0</v>
-      </c>
-      <c r="O199">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -24657,37 +23463,31 @@
         <v>0</v>
       </c>
       <c r="E200">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="F200">
         <v>5</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H200">
         <v>0</v>
       </c>
       <c r="I200">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J200">
         <v>0</v>
       </c>
       <c r="K200">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L200">
-        <v>24</v>
+        <v>-72</v>
       </c>
       <c r="M200">
-        <v>-20</v>
-      </c>
-      <c r="N200">
-        <v>0</v>
-      </c>
-      <c r="O200">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -24704,42 +23504,36 @@
         <v>0</v>
       </c>
       <c r="E201">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="F201">
         <v>5</v>
       </c>
       <c r="G201">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H201">
         <v>0</v>
       </c>
       <c r="I201">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J201">
         <v>0</v>
       </c>
       <c r="K201">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L201">
-        <v>24</v>
+        <v>-73</v>
       </c>
       <c r="M201">
-        <v>-34</v>
-      </c>
-      <c r="N201">
-        <v>0</v>
-      </c>
-      <c r="O201">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O201"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M201"/>
   </ignoredErrors>
 </worksheet>
 </file>